--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.03473211624736</v>
+        <v>3.418143968890196</v>
       </c>
       <c r="D2" t="n">
-        <v>21.28898113176523</v>
+        <v>3.45945943391185</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7874824494496</v>
+        <v>0.7779658980355599</v>
       </c>
       <c r="F2" t="n">
-        <v>4.979960349008864</v>
+        <v>0.8092435567139404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.27739276834709</v>
+        <v>1.832576324856402</v>
       </c>
       <c r="D3" t="n">
-        <v>10.67868570345096</v>
+        <v>1.735286426810781</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7874824494496</v>
+        <v>0.7779658980355599</v>
       </c>
       <c r="F3" t="n">
-        <v>4.979960349008864</v>
+        <v>0.8092435567139404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.78643313430606</v>
+        <v>1.915295384324734</v>
       </c>
       <c r="D4" t="n">
-        <v>11.61538145102584</v>
+        <v>1.887499485791699</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7874824494496</v>
+        <v>0.7779658980355599</v>
       </c>
       <c r="F4" t="n">
-        <v>4.979960349008864</v>
+        <v>0.8092435567139404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.234432551805952</v>
+        <v>1.338095289668467</v>
       </c>
       <c r="D5" t="n">
-        <v>8.183279729150417</v>
+        <v>1.329782955986943</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7874824494496</v>
+        <v>0.7779658980355599</v>
       </c>
       <c r="F5" t="n">
-        <v>4.979960349008864</v>
+        <v>0.8092435567139404</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
